--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_dryandwetbulb.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_dryandwetbulb.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,22 +146,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,9 +165,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -801,11 +789,11 @@
       <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="12" t="n">
-        <v>81.7</v>
+      <c r="G4" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -813,37 +801,37 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="S4" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T4" s="3" t="n">
+      <c r="R4" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="T4" s="9" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="12" t="n">
+      <c r="U4" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="9" t="n">
@@ -852,7 +840,7 @@
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="12" t="n">
+      <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -890,7 +878,7 @@
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -898,53 +886,53 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="17" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+      <c r="M5" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q5" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>2</v>
+      <c r="S5" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>1.4</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X5" s="9" t="n">
+      <c r="W5" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="3" t="n">
         <v>80.5</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>4.4</v>
+      <c r="Z5" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -966,12 +954,12 @@
         <v>25.9</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="G6" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G6" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -981,10 +969,10 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>16.5</v>
+        <v>1.1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>11.1</v>
@@ -993,43 +981,43 @@
         <v>11</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>98.5</v>
+        <v>99.3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q6" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>11.9</v>
+      <c r="S6" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y6" s="3" t="n">
+      <c r="W6" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X6" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y6" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="Z6" s="3" t="n">
-        <v>2.9</v>
+      <c r="Z6" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1066,40 +1054,40 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>21.1</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="M7" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>4.8</v>
+      <c r="S7" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="V7" s="9" t="n">
         <v>18.9</v>
@@ -1107,14 +1095,14 @@
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1136,16 +1124,16 @@
         <v>26.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1153,46 +1141,46 @@
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q8" s="12" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R8" s="3" t="n">
+      <c r="N8" s="9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>6</v>
+      <c r="S8" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="17" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="X8" s="12" t="n">
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1215,7 +1203,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>174.7</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
@@ -1226,11 +1214,11 @@
       <c r="F9" s="9" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>13.9</v>
+      <c r="G9" s="9" t="n">
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>140.6</v>
+        <v>40.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
@@ -1238,14 +1226,14 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="L9" s="18" t="n">
+      <c r="L9" s="10" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="18" t="n">
-        <v>551.2</v>
+      <c r="M9" s="9" t="n">
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>766.1</v>
@@ -1254,14 +1242,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="18" t="n">
+      <c r="Q9" s="9" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="18" t="n">
-        <v>185.3</v>
+      <c r="R9" s="9" t="n">
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1272,14 +1260,14 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="18" t="n">
+      <c r="W9" s="10" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1298,7 +1286,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>25.8</v>
@@ -1318,44 +1306,44 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>9.4</v>
+      <c r="J10" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q10" s="18" t="n">
+      <c r="N10" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="18" t="n">
-        <v>117.7</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.7</v>
+      <c r="R10" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="18" t="n">
+      <c r="W10" s="10" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1379,7 +1367,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
+        <v>509.5</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>27.3</v>
@@ -1390,26 +1378,26 @@
       <c r="F11" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>18.6</v>
+      <c r="G11" s="9" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1420,35 +1408,35 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S11" s="12" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S11" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="T11" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U11" s="12" t="n">
+      <c r="T11" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>9</v>
+      <c r="X11" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="Z11" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1464,7 +1452,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>508.7</v>
+        <v>506.7</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>25.9</v>
@@ -1482,18 +1470,18 @@
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1505,35 +1493,35 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>25.4</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>20.4</v>
+      <c r="S12" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>14.8</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>12.2</v>
+      <c r="W12" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X12" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z12" s="9" t="n">
+        <v>8.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1552,25 +1540,25 @@
         <v>357.9</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>99.40000000000001</v>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.5</v>
@@ -1579,9 +1567,9 @@
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N13" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
@@ -1590,20 +1578,20 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>185.4</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>13</v>
+      <c r="S13" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>19.6</v>
@@ -1637,13 +1625,13 @@
         <v>227</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>10.5</v>
@@ -1651,19 +1639,19 @@
       <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>28.5</v>
+      <c r="I14" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M14" s="12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1673,37 +1661,37 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <v>84.90000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>14.9</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0.6</v>
+        <v>16.7</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X14" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>1</v>
+      <c r="W14" s="9" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X14" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>-0.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1719,19 +1707,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>631</v>
+        <v>31</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>50.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1740,19 +1728,19 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="17" t="n">
-        <v>77.40000000000001</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1760,20 +1748,20 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S15" s="12" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="S15" s="9" t="n">
         <v>15.7</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="12" t="n">
-        <v>17.8</v>
+      <c r="U15" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>20.7</v>
@@ -1807,13 +1795,13 @@
       <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="18" t="n">
-        <v>568.1</v>
-      </c>
-      <c r="F16" s="18" t="n">
+      <c r="E16" s="9" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="9" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1825,26 +1813,26 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M16" s="18" t="n">
+      <c r="L16" s="10" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="M16" s="10" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>489.8</v>
+        <v>89</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="18" t="n">
-        <v>1111</v>
+      <c r="Q16" s="9" t="n">
+        <v>111</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>82.2</v>
@@ -1853,16 +1841,16 @@
         <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>603.9</v>
-      </c>
-      <c r="V16" s="18" t="n">
-        <v>958.2</v>
-      </c>
-      <c r="W16" s="18" t="n">
-        <v>801.9</v>
+        <v>60.9</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1905,56 +1893,56 @@
         <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="18" t="n">
+      <c r="L17" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="18" t="n">
+      <c r="M17" s="10" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Q17" s="18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q17" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>362</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>18.2</v>
+      <c r="S17" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="18" t="n">
+      <c r="W17" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>872.8</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+      <c r="X17" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1958,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>845.5</v>
+        <v>45.5</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>25.9</v>
@@ -1979,21 +1967,21 @@
         <v>10.9</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>13</v>
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L18" s="9" t="n">
@@ -2014,32 +2002,32 @@
       <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S18" s="12" t="n">
+      <c r="R18" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="S18" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="T18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U18" s="12" t="n">
+      <c r="T18" s="9" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U18" s="9" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+      <c r="X18" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z18" s="9" t="n">
+        <v>7.3</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2066,8 +2054,8 @@
       <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>17.9</v>
+      <c r="G19" s="9" t="n">
+        <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2078,10 +2066,10 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2099,17 +2087,17 @@
       <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="R19" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S19" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="9" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="12" t="n">
-        <v>7.2</v>
+      <c r="U19" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>21.2</v>
@@ -2157,59 +2145,59 @@
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>33.3</v>
+      <c r="I20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N20" s="12" t="n">
+      <c r="M20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S20" s="3" t="n">
+      <c r="R20" s="9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S20" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="T20" s="3" t="n">
+      <c r="T20" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="12" t="n">
-        <v>222.4</v>
+      <c r="U20" s="9" t="n">
+        <v>22.4</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>7.6</v>
+      <c r="W20" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y20" s="9" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="Z20" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2230,13 +2218,13 @@
       <c r="D21" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2248,52 +2236,52 @@
       <c r="J21" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P21" s="3" t="n">
+      <c r="O21" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P21" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S21" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>1.6</v>
+      <c r="U21" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X21" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Y21" s="3" t="n">
+      <c r="W21" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Z21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2310,22 +2298,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>989</v>
+        <v>9</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="17" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>83.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
@@ -2333,53 +2321,53 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="12" t="n">
+      <c r="K22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P22" s="3" t="n">
+      <c r="N22" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S22" s="3" t="n">
+      <c r="R22" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S22" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="U22" s="3" t="n">
+      <c r="T22" s="9" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="U22" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>139.7</v>
+      <c r="X22" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y22" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z22" s="9" t="n">
+        <v>9.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2395,55 +2383,55 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2322.3</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F23" s="18" t="n">
+        <v>2320.3</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F23" s="9" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+      <c r="G23" s="9" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K23" s="18" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="18" t="n">
+      <c r="L23" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="18" t="n">
-        <v>161.8</v>
+      <c r="M23" s="10" t="n">
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
+        <v>93</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="18" t="n">
-        <v>85</v>
+      <c r="R23" s="9" t="n">
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2454,7 +2442,7 @@
       <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="18" t="n">
+      <c r="W23" s="9" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2501,19 +2489,19 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L24" s="18" t="n">
+      <c r="L24" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="18" t="n">
+      <c r="M24" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2524,32 +2512,32 @@
       <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="18" t="n">
+      <c r="R24" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>17.8</v>
+      <c r="S24" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>13.1</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="18" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="W24" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X24" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2576,8 +2564,8 @@
       <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>10.9</v>
+      <c r="G25" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
@@ -2588,23 +2576,23 @@
       <c r="J25" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>6.4</v>
+      <c r="K25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>24.7</v>
@@ -2650,7 +2638,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>349.1</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>24.4</v>
@@ -2667,29 +2655,29 @@
       <c r="H26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>23.4</v>
+      <c r="I26" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0.9</v>
+      <c r="N26" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>21</v>
@@ -2709,17 +2697,17 @@
       <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X26" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y26" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="Z26" s="9" t="n">
-        <v>8.199999999999999</v>
+      <c r="W26" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2738,16 +2726,16 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>24</v>
+      <c r="G27" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.4</v>
@@ -2756,25 +2744,25 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0.4</v>
+      <c r="N27" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>17.6</v>
@@ -2794,17 +2782,17 @@
       <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y27" s="9" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>0.9</v>
+      <c r="X27" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2831,11 +2819,11 @@
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>15.9</v>
+      <c r="G28" s="9" t="n">
+        <v>15.5</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.4</v>
@@ -2843,11 +2831,11 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>13.3</v>
@@ -2856,10 +2844,10 @@
         <v>15.3</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>98.7</v>
+        <v>99.3</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>22.9</v>
@@ -2879,17 +2867,17 @@
       <c r="V28" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y28" s="9" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Z28" s="9" t="n">
-        <v>1</v>
+      <c r="X28" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,7 +2893,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>28.8</v>
@@ -2916,8 +2904,8 @@
       <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>1.8</v>
+      <c r="G29" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2928,23 +2916,23 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>2.6</v>
+      <c r="N29" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>27</v>
@@ -2965,16 +2953,16 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>17.3</v>
+        <v>14.7</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>71.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2992,16 +2980,16 @@
       <c r="C30" s="3" t="n">
         <v>228.4</v>
       </c>
-      <c r="D30" s="18" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>527.1</v>
+      <c r="D30" s="9" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>52.1</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="9" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -3013,14 +3001,14 @@
       <c r="J30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="K30" s="18" t="n">
+      <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="L30" s="18" t="n">
+      <c r="L30" s="9" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="18" t="n">
-        <v>56.7</v>
+      <c r="M30" s="9" t="n">
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
@@ -3031,7 +3019,7 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="18" t="n">
+      <c r="Q30" s="10" t="n">
         <v>413.2</v>
       </c>
       <c r="R30" s="9" t="n">
@@ -3041,25 +3029,25 @@
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>314.8</v>
+        <v>14.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>522</v>
-      </c>
-      <c r="Y30" s="9" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="Z30" s="9" t="n">
-        <v>506.8</v>
+      <c r="X30" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>35</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3075,7 +3063,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>26.2</v>
@@ -3099,50 +3087,50 @@
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>11.5</v>
+      <c r="L31" s="10" t="n">
+        <v>11.9</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="P31" s="9" t="n">
+      <c r="N31" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="18" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="U31" s="12" t="n">
-        <v>111.4</v>
+      <c r="R31" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>7.7</v>
       </c>
       <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y31" s="9" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="Z31" s="9" t="n">
-        <v>4.6</v>
+      <c r="X31" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>730.2</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3167,7 +3155,7 @@
         <v>10.2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>17.7</v>
@@ -3181,11 +3169,11 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>20.5</v>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>10.2</v>
@@ -3193,39 +3181,39 @@
       <c r="N32" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O32" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>26.46</v>
+      <c r="O32" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T32" s="9" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="V32" s="3" t="n">
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="n">
-        <v>171.8</v>
+      <c r="X32" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y32" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Z32" s="9" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3256,61 +3244,61 @@
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q33" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>19.9</v>
+      <c r="S33" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>19.4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v>14</v>
+      <c r="X33" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Y33" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z33" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3326,7 +3314,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>23.3</v>
@@ -3340,62 +3328,62 @@
       <c r="G34" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H34" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O34" s="3" t="n">
+      <c r="N34" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O34" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="P34" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="S34" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T34" s="9" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="U34" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>28.7</v>
+      <c r="S34" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>3.8</v>
+      <c r="X34" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y34" s="9" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="Z34" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3434,7 +3422,7 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
@@ -3444,43 +3432,43 @@
         <v>12.9</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q35" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T35" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="V35" s="12" t="n">
+      <c r="S35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V35" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>8</v>
+      <c r="X35" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="Z35" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3502,70 +3490,70 @@
         <v>26.3</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G36" s="9" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>8.6</v>
+      <c r="K36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>10.6</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T36" s="9" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="U36" s="9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V36" s="3" t="n">
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="V36" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>11</v>
+      <c r="X36" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Z36" s="9" t="n">
+        <v>7.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3581,7 +3569,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>224.4</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
@@ -3592,60 +3580,60 @@
       <c r="F37" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>62.6</v>
+      <c r="G37" s="9" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L37" s="18" t="n">
-        <v>63</v>
-      </c>
-      <c r="M37" s="18" t="n">
+      <c r="K37" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="M37" s="9" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492</v>
+        <v>92</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="18" t="n">
+      <c r="Q37" s="10" t="n">
         <v>115.5</v>
       </c>
-      <c r="R37" s="18" t="n">
-        <v>89.90000000000001</v>
+      <c r="R37" s="10" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>16.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="18" t="n">
+      <c r="V37" s="9" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="18" t="n">
+      <c r="W37" s="10" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.3</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>34.6</v>
@@ -3664,7 +3652,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.8</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>25.7</v>
@@ -3684,10 +3672,12 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="9" t="n">
         <v>13</v>
       </c>
@@ -3698,40 +3688,40 @@
         <v>14.8</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T38" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="U38" s="9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="V38" s="18" t="n">
+      <c r="S38" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>6.9</v>
+      <c r="X38" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y38" s="9" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="Z38" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3762,59 +3752,59 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M39" s="9" t="n">
+      <c r="L39" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="12" t="n">
+      <c r="N39" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q39" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V39" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W39" s="17" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v>176</v>
+      <c r="V39" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="9" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Y39" s="9" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="Z39" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3830,7 +3820,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>27.2</v>
@@ -3853,53 +3843,53 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>10.2</v>
+      <c r="N40" s="9" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P40" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S40" s="12" t="n">
+      <c r="R40" s="9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S40" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="T40" s="3" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="U40" s="3" t="n">
+      <c r="T40" s="9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="U40" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W40" s="12" t="n">
+      <c r="V40" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="W40" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y40" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>83</v>
+      <c r="X40" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="Z40" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3918,51 +3908,51 @@
         <v>451.2</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>28.94</v>
+        <v>28.4</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G41" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G41" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>51</v>
+      <c r="H41" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="9" t="n">
-        <v>11.1</v>
+      <c r="N41" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q41" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="12" t="n">
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
@@ -3971,20 +3961,20 @@
       <c r="U41" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="17" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>15.7</v>
+      <c r="W41" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X41" s="9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Y41" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Z41" s="9" t="n">
+        <v>5.1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4005,34 +3995,34 @@
       <c r="D42" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="17" t="n">
-        <v>1.1</v>
+      <c r="E42" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="17" t="n">
-        <v>12.6</v>
+      <c r="G42" s="9" t="n">
+        <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M42" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N42" s="9" t="n">
+      <c r="L42" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N42" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4041,25 +4031,25 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R42" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S42" s="12" t="n">
+      <c r="Q42" s="14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R42" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U42" s="12" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="16" t="inlineStr"/>
+      <c r="W42" s="9" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4080,25 +4070,25 @@
         <v>0.1</v>
       </c>
       <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
-      <c r="L43" s="16" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="16" t="inlineStr"/>
+      <c r="Q43" s="13" t="inlineStr"/>
+      <c r="R43" s="9" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="16" t="inlineStr"/>
-      <c r="W43" s="16" t="inlineStr"/>
+      <c r="V43" s="9" t="inlineStr"/>
+      <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4119,25 +4109,25 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="16" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="16" t="inlineStr"/>
+      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="16" t="inlineStr"/>
-      <c r="W44" s="16" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4155,36 +4145,36 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1981.2</v>
-      </c>
-      <c r="D45" s="18" t="n">
+        <v>1911.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
         <v>109.7</v>
       </c>
-      <c r="E45" s="18" t="n">
-        <v>41.8</v>
+      <c r="E45" s="9" t="n">
+        <v>41.5</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="17" t="n">
-        <v>10.8</v>
+      <c r="G45" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L45" s="18" t="n">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="18" t="n">
+      <c r="M45" s="10" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4194,12 +4184,12 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Q45" s="18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" s="10" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="18" t="n">
+      <c r="R45" s="9" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4211,14 +4201,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="18" t="n">
-        <v>831.9</v>
-      </c>
-      <c r="W45" s="18" t="n">
+      <c r="V45" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="W45" s="10" t="n">
         <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4261,33 +4251,33 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L46" s="18" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="M46" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>111100</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M46" s="10" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q46" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q46" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="18" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="12" t="n">
+      <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
@@ -4296,20 +4286,20 @@
       <c r="U46" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V46" s="18" t="n">
+      <c r="V46" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="18" t="n">
+      <c r="W46" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>265.7</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>81.90000000000001</v>
+      <c r="X46" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y46" s="9" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Z46" s="9" t="n">
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_dryandwetbulb.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_dryandwetbulb.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -162,9 +162,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -805,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M4" s="9" t="n">
         <v>9.1</v>
@@ -814,10 +811,10 @@
         <v>11.6</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>95.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>25.8</v>
@@ -837,17 +834,17 @@
       <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+      <c r="X4" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z4" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -922,17 +919,17 @@
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>2.9</v>
+      <c r="W5" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X5" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="Z5" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -963,7 +960,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -1054,7 +1051,7 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.1</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -1092,17 +1089,17 @@
       <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+      <c r="X7" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>2.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1136,7 +1133,7 @@
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
@@ -1177,17 +1174,17 @@
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>2.6</v>
+      <c r="X8" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1203,7 +1200,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.7</v>
+        <v>174.9</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
@@ -1229,7 +1226,7 @@
       <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="9" t="n">
         <v>56.7</v>
       </c>
       <c r="M9" s="9" t="n">
@@ -1249,7 +1246,7 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1260,14 +1257,14 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="9" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1328,31 +1325,33 @@
       <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S10" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T10" s="9" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v>4.3</v>
+      <c r="R10" s="10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>6.7</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="X10" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1367,7 +1366,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
+        <v>509.3</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>27.3</v>
@@ -1390,7 +1389,7 @@
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1412,31 +1411,31 @@
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>12.4</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>14.4</v>
+        <v>19.5</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>42</v>
+        <v>56.9</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>19.9</v>
+        <v>14.7</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X11" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="9" t="n">
-        <v>20.1</v>
-      </c>
       <c r="Y11" s="9" t="n">
-        <v>75.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1475,7 +1474,7 @@
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1511,17 +1510,17 @@
       <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X12" s="9" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>8.6</v>
+      <c r="W12" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1555,12 +1554,12 @@
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1576,7 +1575,7 @@
         <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>18.9</v>
@@ -1643,13 +1642,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>6.7</v>
+        <v>11.5</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>16.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1681,17 +1680,17 @@
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="9" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X14" s="9" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>-0.8</v>
+      <c r="W14" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1707,7 +1706,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>31</v>
+        <v>631</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>26</v>
@@ -1730,7 +1729,7 @@
       <c r="J15" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1796,12 +1795,12 @@
         <v>128</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1813,7 +1812,7 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="9" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -1826,7 +1825,7 @@
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
@@ -1896,7 +1895,7 @@
         <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>27.4</v>
+        <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="10" t="n">
@@ -1912,7 +1911,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>22.2</v>
@@ -1932,17 +1931,17 @@
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Y17" s="9" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="Z17" s="9" t="n">
-        <v>4.5</v>
+      <c r="X17" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1976,7 +1975,7 @@
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -2167,7 +2166,7 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>28</v>
@@ -2234,22 +2233,22 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>13.1</v>
+        <v>17.6</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>13</v>
+        <v>17.4</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>0.2</v>
@@ -2298,13 +2297,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9</v>
+        <v>429</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>18.7</v>
@@ -2401,7 +2400,7 @@
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>20.8</v>
@@ -2419,10 +2418,10 @@
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
@@ -2489,10 +2488,10 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>22.1</v>
+        <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>12.5</v>
@@ -2501,7 +2500,7 @@
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2571,10 +2570,10 @@
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
@@ -2659,7 +2658,7 @@
         <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0.9</v>
@@ -2698,10 +2697,10 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>13.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>142.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
@@ -2744,7 +2743,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>7.1</v>
@@ -2814,13 +2813,13 @@
         <v>27</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.1</v>
@@ -2904,8 +2903,8 @@
       <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>18.7</v>
+      <c r="G29" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2938,16 +2937,16 @@
         <v>27</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="S29" s="9" t="n">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>47.8</v>
+        <v>60.4</v>
       </c>
       <c r="U29" s="9" t="n">
-        <v>18.6</v>
+        <v>14.1</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>22.8</v>
@@ -2978,7 +2977,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>228.4</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>131.2</v>
@@ -2993,7 +2992,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3029,7 +3028,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>14.8</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>55.4</v>
@@ -3093,8 +3092,8 @@
       <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>12.4</v>
+      <c r="N31" s="9" t="n">
+        <v>13.2</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3130,7 +3129,7 @@
         <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>25.8</v>
+        <v>165.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3190,7 @@
         <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
@@ -3329,7 +3328,7 @@
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.5</v>
@@ -3344,10 +3343,10 @@
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="O34" s="9" t="n">
         <v>99</v>
@@ -3450,7 +3449,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
@@ -3538,7 +3537,7 @@
         <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="V36" s="9" t="n">
         <v>20.6</v>
@@ -3569,7 +3568,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>224.4</v>
+        <v>224</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
@@ -3584,7 +3583,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>14.1</v>
@@ -3605,20 +3604,20 @@
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>92</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
       <c r="Q37" s="10" t="n">
         <v>115.5</v>
       </c>
       <c r="R37" s="10" t="n">
-        <v>89.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>16.4</v>
+        <v>316.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
@@ -3630,7 +3629,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3673,7 +3672,7 @@
         <v>28.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>42.1</v>
+        <v>22.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3706,7 +3705,7 @@
         <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="9" t="n">
         <v>20.2</v>
@@ -3740,7 +3739,7 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="E39" s="9" t="n">
         <v>11</v>
@@ -3752,7 +3751,7 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.5</v>
@@ -3766,30 +3765,32 @@
       <c r="L39" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q39" s="3" t="n">
+      <c r="N39" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>19</v>
+      <c r="S39" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T39" s="9" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>14.2</v>
       </c>
       <c r="V39" s="9" t="n">
         <v>21.7</v>
@@ -3853,13 +3854,13 @@
         <v>10.3</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>98.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>22</v>
@@ -3920,7 +3921,7 @@
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
@@ -3934,32 +3935,32 @@
       <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+      <c r="N41" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P41" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q41" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>12.9</v>
+      <c r="S41" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>8.9</v>
       </c>
       <c r="V41" s="9" t="n">
         <v>22</v>
@@ -4019,32 +4020,32 @@
       <c r="L42" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q42" s="14" t="n">
-        <v>2.6</v>
+      <c r="M42" s="9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="P42" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>26.6</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>19.6</v>
+      <c r="S42" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T42" s="9" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>14.7</v>
       </c>
       <c r="V42" s="9" t="n">
         <v>22</v>
@@ -4078,11 +4079,11 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="13" t="inlineStr"/>
+      <c r="Q43" s="9" t="inlineStr"/>
       <c r="R43" s="9" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -4117,11 +4118,11 @@
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
       <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -4157,10 +4158,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>27.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4174,19 +4175,19 @@
       <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="M45" s="9" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>5.1</v>
+        <v>51.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="R45" s="9" t="n">
@@ -4251,18 +4252,18 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.2</v>
+        <v>52.1</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>111100</v>
+        <v>101.1</v>
       </c>
       <c r="L46" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4271,20 +4272,20 @@
       <c r="P46" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>14.7</v>
+      <c r="S46" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="T46" s="9" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>10.9</v>
       </c>
       <c r="V46" s="9" t="n">
         <v>21.3</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_dryandwetbulb.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_dryandwetbulb.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,16 +146,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -777,16 +768,16 @@
       <c r="C4" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -798,53 +789,53 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M4" s="9" t="n">
+      <c r="L4" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="O4" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P4" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q4" s="9" t="n">
+      <c r="O4" s="8" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q4" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="8" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y4" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z4" s="9" t="n">
-        <v>5.6</v>
+      <c r="X4" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -862,16 +853,16 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -883,53 +874,53 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="N5" s="9" t="n">
+      <c r="N5" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" s="8" t="n">
         <v>94.2</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="P5" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" s="8" t="n">
         <v>1.4</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X5" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y5" s="9" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="Z5" s="9" t="n">
-        <v>3</v>
+      <c r="W5" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -947,16 +938,16 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -968,52 +959,52 @@
       <c r="J6" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="8" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="Z6" s="8" t="n">
         <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1032,16 +1023,16 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1051,55 +1042,55 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K7" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="N7" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="O7" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P7" s="9" t="n">
+      <c r="P7" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="8" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y7" s="9" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="Z7" s="9" t="n">
-        <v>2.7</v>
+      <c r="X7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1117,74 +1108,74 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P8" s="9" t="n">
+      <c r="P8" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="8" t="n">
         <v>4.3</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Y8" s="9" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="Z8" s="9" t="n">
-        <v>1.8</v>
+      <c r="X8" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1200,18 +1191,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1223,13 +1214,13 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="8" t="n">
         <v>7.7</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1239,14 +1230,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="8" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1254,7 +1245,7 @@
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>95</v>
       </c>
       <c r="W9" s="9" t="n">
@@ -1285,16 +1276,16 @@
       <c r="C10" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1307,51 +1298,49 @@
         <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="10" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="V10" s="9" t="n">
+      <c r="R10" s="8" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V10" s="8" t="n">
         <v>19</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y10" s="9" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Z10" s="9" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="X10" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1366,18 +1355,18 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>504.5</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1389,14 +1378,14 @@
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1407,34 +1396,34 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="R11" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S11" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T11" s="9" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="U11" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V11" s="9" t="n">
+      <c r="R11" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="Z11" s="9" t="n">
+      <c r="Z11" s="8" t="n">
         <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1453,16 +1442,16 @@
       <c r="C12" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1474,7 +1463,7 @@
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1492,26 +1481,26 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S12" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T12" s="9" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V12" s="9" t="n">
+      <c r="R12" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V12" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.7</v>
+        <v>14.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
@@ -1538,35 +1527,35 @@
       <c r="C13" s="3" t="n">
         <v>357.9</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
+        <v>18.6</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>13.6</v>
@@ -1577,34 +1566,34 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="8" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="8" t="n">
         <v>2.1</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X13" s="9" t="n">
+      <c r="X13" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="Z13" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1623,16 +1612,16 @@
       <c r="C14" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1642,13 +1631,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>16.7</v>
+        <v>8.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.2</v>
+        <v>13.3</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1662,22 +1651,22 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1708,16 +1697,16 @@
       <c r="C15" s="3" t="n">
         <v>631</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1729,7 +1718,7 @@
       <c r="J15" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1747,34 +1736,34 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1791,13 +1780,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="8" t="n">
         <v>92.5</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1815,10 +1804,10 @@
       <c r="K16" s="9" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" s="9" t="n">
         <v>59.1</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="9" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1830,10 +1819,10 @@
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="8" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1845,10 +1834,10 @@
       <c r="U16" s="3" t="n">
         <v>60.9</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>98.2</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="9" t="n">
         <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1876,16 +1865,16 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1898,10 +1887,10 @@
         <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1911,27 +1900,27 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="S17" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="T17" s="9" t="n">
+      <c r="T17" s="8" t="n">
         <v>69.7</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="U17" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="9" t="n">
         <v>16.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1941,7 +1930,7 @@
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1959,73 +1948,73 @@
       <c r="C18" s="3" t="n">
         <v>45.5</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="P18" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="8" t="n">
         <v>46.2</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="9" t="n">
+      <c r="X18" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="8" t="n">
         <v>70.8</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="Z18" s="8" t="n">
         <v>7.3</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2044,16 +2033,16 @@
       <c r="C19" s="3" t="n">
         <v>531.1</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2065,10 +2054,10 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2083,34 +2072,34 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="8" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="Y19" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="8" t="n">
         <v>6.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2129,16 +2118,16 @@
       <c r="C20" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2150,10 +2139,10 @@
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2166,36 +2155,36 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q20" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S20" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T20" s="8" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="X20" s="9" t="n">
+      <c r="X20" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="Y20" s="9" t="n">
+      <c r="Y20" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="Z20" s="9" t="n">
+      <c r="Z20" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2212,18 +2201,18 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>382.4</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2233,54 +2222,54 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K21" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="9" t="n">
+      <c r="N21" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="O21" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="P21" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="S21" s="9" t="n">
+      <c r="S21" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="9" t="n">
+      <c r="T21" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>17.5</v>
       </c>
-      <c r="X21" s="9" t="n">
+      <c r="X21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="Y21" s="9" t="n">
+      <c r="Y21" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="Z21" s="9" t="n">
+      <c r="Z21" s="8" t="n">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2297,18 +2286,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
-      </c>
-      <c r="D22" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2320,52 +2309,52 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="S22" s="9" t="n">
+      <c r="S22" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="T22" s="9" t="n">
+      <c r="T22" s="8" t="n">
         <v>49.5</v>
       </c>
-      <c r="U22" s="9" t="n">
+      <c r="U22" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="9" t="n">
+      <c r="X22" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="Y22" s="9" t="n">
+      <c r="Y22" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="Z22" s="9" t="n">
+      <c r="Z22" s="8" t="n">
         <v>9.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -2382,18 +2371,18 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>232</v>
+      </c>
+      <c r="D23" s="8" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>56.7</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2405,13 +2394,13 @@
       <c r="J23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="9" t="n">
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2421,12 +2410,12 @@
         <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q23" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="8" t="n">
         <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2438,10 +2427,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2469,16 +2458,16 @@
       <c r="C24" s="3" t="n">
         <v>464.1</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2491,16 +2480,16 @@
         <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.8</v>
+        <v>10.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2508,34 +2497,34 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="9" t="n">
+      <c r="S24" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T24" s="9" t="n">
+      <c r="T24" s="8" t="n">
         <v>60.5</v>
       </c>
-      <c r="U24" s="9" t="n">
+      <c r="U24" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="X24" s="9" t="n">
+      <c r="X24" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y24" s="9" t="n">
+      <c r="Y24" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="Z24" s="9" t="n">
+      <c r="Z24" s="8" t="n">
         <v>5.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -2554,16 +2543,16 @@
       <c r="C25" s="3" t="n">
         <v>488.9</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2575,52 +2564,52 @@
       <c r="J25" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O25" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P25" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q25" s="9" t="n">
+      <c r="K25" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="Z25" s="9" t="n">
+      <c r="Z25" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -2639,16 +2628,16 @@
       <c r="C26" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
@@ -2660,53 +2649,53 @@
       <c r="J26" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="N26" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="O26" s="9" t="n">
+      <c r="O26" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P26" s="9" t="n">
+      <c r="P26" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="9" t="n">
+      <c r="S26" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="T26" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="U26" s="9" t="n">
+      <c r="U26" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>142.2</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>11.8</v>
+      <c r="W26" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y26" s="8" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="Z26" s="8" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2724,16 +2713,16 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>25.1</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2745,53 +2734,53 @@
       <c r="J27" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="S27" s="9" t="n">
+      <c r="S27" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="8" t="n">
         <v>90.3</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>1.6</v>
+      <c r="X27" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="Z27" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2809,16 +2798,16 @@
       <c r="C28" s="3" t="n">
         <v>513.3</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2830,53 +2819,53 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="9" t="n">
+      <c r="N28" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="O28" s="9" t="n">
+      <c r="O28" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P28" s="9" t="n">
+      <c r="P28" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" s="8" t="n">
         <v>76.7</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>1.8</v>
+      <c r="X28" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Z28" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2894,17 +2883,17 @@
       <c r="C29" s="3" t="n">
         <v>593.3</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2915,52 +2904,52 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="8" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S29" s="9" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="U29" s="9" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="V29" s="9" t="n">
+      <c r="R29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V29" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="X29" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="Y29" s="9" t="n">
+      <c r="Y29" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="Z29" s="9" t="n">
+      <c r="Z29" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -2977,22 +2966,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>131.2</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>52.1</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3003,10 +2992,10 @@
       <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="L30" s="9" t="n">
+      <c r="L30" s="8" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="8" t="n">
         <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3018,10 +3007,10 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="9" t="n">
         <v>413.2</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3033,10 +3022,10 @@
       <c r="U30" s="3" t="n">
         <v>55.4</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="8" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3064,16 +3053,16 @@
       <c r="C31" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3086,14 +3075,14 @@
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="9" t="n">
-        <v>13.2</v>
+      <c r="N31" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3101,35 +3090,35 @@
       <c r="P31" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S31" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U31" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>730.2</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>165.8</v>
+      <c r="X31" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y31" s="8" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Z31" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3147,16 +3136,16 @@
       <c r="C32" s="3" t="n">
         <v>520</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3168,50 +3157,50 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="N32" s="9" t="n">
+      <c r="N32" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="O32" s="9" t="n">
+      <c r="O32" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P32" s="9" t="n">
+      <c r="P32" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="9" t="n">
+      <c r="X32" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y32" s="9" t="n">
+      <c r="Y32" s="8" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="Z32" s="9" t="n">
+      <c r="Z32" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -3230,16 +3219,16 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3251,28 +3240,28 @@
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="N33" s="9" t="n">
+      <c r="N33" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="O33" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P33" s="9" t="n">
+      <c r="P33" s="8" t="n">
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3284,19 +3273,19 @@
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Y33" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="Z33" s="9" t="n">
+      <c r="Z33" s="8" t="n">
         <v>2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -3315,16 +3304,16 @@
       <c r="C34" s="3" t="n">
         <v>329.1</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3336,28 +3325,28 @@
       <c r="J34" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="O34" s="9" t="n">
+      <c r="O34" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" s="8" t="n">
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3369,19 +3358,19 @@
       <c r="U34" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="8" t="n">
         <v>88.7</v>
       </c>
-      <c r="Z34" s="9" t="n">
+      <c r="Z34" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -3400,16 +3389,16 @@
       <c r="C35" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3421,52 +3410,52 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="N35" s="9" t="n">
+      <c r="N35" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="O35" s="9" t="n">
+      <c r="O35" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="P35" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="9" t="n">
+      <c r="X35" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="Y35" s="9" t="n">
+      <c r="Y35" s="8" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="Z35" s="9" t="n">
+      <c r="Z35" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -3485,16 +3474,16 @@
       <c r="C36" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3506,52 +3495,52 @@
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="O36" s="9" t="n">
+      <c r="O36" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="9" t="n">
+      <c r="X36" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="Y36" s="9" t="n">
+      <c r="Y36" s="8" t="n">
         <v>68.5</v>
       </c>
-      <c r="Z36" s="9" t="n">
+      <c r="Z36" s="8" t="n">
         <v>7.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -3570,16 +3559,16 @@
       <c r="C37" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" s="8" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3591,13 +3580,13 @@
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>8.5</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3607,10 +3596,10 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="9" t="n">
         <v>115.5</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="9" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3622,14 +3611,14 @@
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="9" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>82.7</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3653,23 +3642,23 @@
       <c r="C38" s="3" t="n">
         <v>448.1</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>28.1</v>
+        <v>2.8</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>22.1</v>
@@ -3677,25 +3666,25 @@
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3707,19 +3696,19 @@
       <c r="U38" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="9" t="n">
+      <c r="X38" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="Y38" s="9" t="n">
+      <c r="Y38" s="8" t="n">
         <v>79.8</v>
       </c>
-      <c r="Z38" s="9" t="n">
+      <c r="Z38" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -3738,16 +3727,16 @@
       <c r="C39" s="3" t="n">
         <v>579.9</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="D39" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -3759,52 +3748,52 @@
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="O39" s="9" t="n">
+      <c r="O39" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="P39" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="S39" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="T39" s="9" t="n">
+      <c r="T39" s="8" t="n">
         <v>59.2</v>
       </c>
-      <c r="U39" s="9" t="n">
+      <c r="U39" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="V39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Y39" s="8" t="n">
         <v>68.7</v>
       </c>
-      <c r="Z39" s="9" t="n">
+      <c r="Z39" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -3823,13 +3812,13 @@
       <c r="C40" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3844,52 +3833,52 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="8" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="9" t="n">
+      <c r="N40" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="O40" s="9" t="n">
+      <c r="O40" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="P40" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="S40" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="8" t="n">
         <v>69.5</v>
       </c>
-      <c r="U40" s="9" t="n">
+      <c r="U40" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y40" s="9" t="n">
+      <c r="Y40" s="8" t="n">
         <v>83.3</v>
       </c>
-      <c r="Z40" s="9" t="n">
+      <c r="Z40" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -3908,16 +3897,16 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3929,52 +3918,52 @@
       <c r="J41" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="P41" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="U41" s="9" t="n">
+      <c r="U41" s="8" t="n">
         <v>8.9</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="Y41" s="9" t="n">
+      <c r="Y41" s="8" t="n">
         <v>80.5</v>
       </c>
-      <c r="Z41" s="9" t="n">
+      <c r="Z41" s="8" t="n">
         <v>5.1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -3993,16 +3982,16 @@
       <c r="C42" s="3" t="n">
         <v>524.4</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4014,43 +4003,43 @@
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="8" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="8" t="n">
         <v>57.7</v>
       </c>
-      <c r="U42" s="9" t="n">
+      <c r="U42" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="9" t="inlineStr"/>
+      <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4068,28 +4057,28 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="9" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
+      <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="9" t="inlineStr"/>
-      <c r="W43" s="9" t="inlineStr"/>
+      <c r="V43" s="8" t="inlineStr"/>
+      <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4107,28 +4096,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4146,22 +4135,22 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>109.7</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <v>41.5</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4169,13 +4158,13 @@
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="8" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4185,12 +4174,12 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4202,14 +4191,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="W45" s="10" t="n">
+      <c r="W45" s="9" t="n">
         <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>66.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4233,16 +4222,16 @@
       <c r="C46" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4252,18 +4241,18 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="L46" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4272,34 +4261,34 @@
       <c r="P46" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="9" t="n">
+      <c r="S46" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="T46" s="9" t="n">
+      <c r="T46" s="8" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="U46" s="9" t="n">
+      <c r="U46" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="9" t="n">
+      <c r="X46" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y46" s="9" t="n">
+      <c r="Y46" s="8" t="n">
         <v>75.5</v>
       </c>
-      <c r="Z46" s="9" t="n">
+      <c r="Z46" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_dryandwetbulb.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_dryandwetbulb.xlsx
@@ -146,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -799,19 +799,19 @@
         <v>9.1</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>95.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
         <v>14.1</v>
@@ -884,13 +884,13 @@
         <v>11.4</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>94.2</v>
+        <v>90</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>19.6</v>
@@ -899,13 +899,13 @@
         <v>18.6</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>19.5</v>
@@ -972,10 +972,10 @@
         <v>13.1</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>15.4</v>
@@ -984,22 +984,22 @@
         <v>14.7</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>95.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="Y6" s="8" t="n">
         <v>95</v>
@@ -1054,13 +1054,13 @@
         <v>13.1</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>19.3</v>
@@ -1069,27 +1069,27 @@
         <v>16.8</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>19.1</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>85.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="3" t="n">
+      <c r="X7" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y7" s="8" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="Z7" s="8" t="n">
         <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1139,13 +1139,13 @@
         <v>10.6</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>98.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q8" s="8" t="n">
         <v>21.4</v>
@@ -1154,27 +1154,27 @@
         <v>18.4</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>21.2</v>
+        <v>19.1</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="V8" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z8" s="3" t="n">
+      <c r="X8" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y8" s="8" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="Z8" s="8" t="n">
         <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1305,13 +1305,13 @@
         <v>11</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>98</v>
+        <v>96.5</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>20.3</v>
@@ -1320,13 +1320,13 @@
         <v>17.1</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>19</v>
@@ -1400,7 +1400,7 @@
         <v>26.3</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>12.4</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="8" t="n">
         <v>14.4</v>
@@ -1414,8 +1414,8 @@
       <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>15.5</v>
+      <c r="W11" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="X11" s="8" t="n">
         <v>17.6</v>
@@ -1485,7 +1485,7 @@
         <v>25.4</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>12.1</v>
@@ -1573,19 +1573,19 @@
         <v>17.3</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>19.7</v>
+        <v>18.6</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>90.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="V13" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>16.8</v>
+      <c r="W13" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>19.1</v>
@@ -1658,13 +1658,13 @@
         <v>14.7</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>98.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="V14" s="8" t="n">
         <v>14.5</v>
@@ -1740,7 +1740,7 @@
         <v>25.5</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>13.7</v>
+        <v>17.6</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>15.7</v>
@@ -1754,8 +1754,8 @@
       <c r="V15" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>14.4</v>
+      <c r="W15" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="X15" s="8" t="n">
         <v>16.4</v>
@@ -1909,13 +1909,13 @@
         <v>16.4</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>18.6</v>
+        <v>14.7</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>69.7</v>
+        <v>54.9</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>8.1</v>
+        <v>12.1</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>19.6</v>
@@ -1975,8 +1975,8 @@
       <c r="L18" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>14.5</v>
+      <c r="M18" s="10" t="n">
+        <v>1.6</v>
       </c>
       <c r="N18" s="8" t="n">
         <v>16.5</v>
@@ -1991,7 +1991,7 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>13.4</v>
+        <v>17.5</v>
       </c>
       <c r="S18" s="8" t="n">
         <v>15.4</v>
@@ -2009,13 +2009,13 @@
         <v>15.5</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>17.6</v>
+        <v>13.9</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>70.8</v>
+        <v>55.7</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2060,23 +2060,23 @@
       <c r="L19" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="N19" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P19" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>14.2</v>
+        <v>18</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>16.2</v>
@@ -2091,7 +2091,7 @@
         <v>21.2</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>16.4</v>
+        <v>17.8</v>
       </c>
       <c r="X19" s="8" t="n">
         <v>18.6</v>
@@ -2145,23 +2145,23 @@
       <c r="L20" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="n">
+      <c r="N20" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P20" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="8" t="n">
         <v>28</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>13.3</v>
+        <v>18.1</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>15.3</v>
@@ -2179,13 +2179,13 @@
         <v>18.4</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>21.2</v>
+        <v>18.6</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>79.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2230,8 +2230,8 @@
       <c r="L21" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>17.4</v>
+      <c r="M21" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>19.9</v>
@@ -2246,7 +2246,7 @@
         <v>25.6</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>14.8</v>
+        <v>18.2</v>
       </c>
       <c r="S21" s="8" t="n">
         <v>16.8</v>
@@ -2261,7 +2261,7 @@
         <v>19.8</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="X21" s="8" t="n">
         <v>20</v>
@@ -2331,7 +2331,7 @@
         <v>23.6</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>12.4</v>
+        <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>14.4</v>
@@ -2349,13 +2349,13 @@
         <v>15.6</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>17.7</v>
+        <v>13</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>65</v>
+        <v>47.8</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>9.5</v>
+        <v>14.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2485,16 +2485,16 @@
       <c r="L24" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="P24" s="3" t="n">
+      <c r="N24" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P24" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="Q24" s="8" t="n">
@@ -2504,13 +2504,13 @@
         <v>17.6</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>20.1</v>
+        <v>14.5</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>60.5</v>
+        <v>43.7</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>13.1</v>
+        <v>18.7</v>
       </c>
       <c r="V24" s="8" t="n">
         <v>21.3</v>
@@ -2519,13 +2519,13 @@
         <v>17.1</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>19.5</v>
+        <v>16.6</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>77</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>17</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>16.7</v>
+        <v>9.9</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>19</v>
@@ -2589,19 +2589,19 @@
         <v>17.2</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>19.6</v>
+        <v>14.5</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>63</v>
+        <v>46.6</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>11.5</v>
+        <v>16.6</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>14.8</v>
+        <v>16.9</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>16.8</v>
@@ -2659,13 +2659,13 @@
         <v>10.2</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>98.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q26" s="8" t="n">
         <v>21</v>
@@ -2674,13 +2674,13 @@
         <v>16.2</v>
       </c>
       <c r="S26" s="8" t="n">
-        <v>18.4</v>
+        <v>15.1</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>74</v>
+        <v>60.9</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="V26" s="8" t="n">
         <v>21.6</v>
@@ -2689,13 +2689,13 @@
         <v>15.5</v>
       </c>
       <c r="X26" s="8" t="n">
-        <v>17.6</v>
+        <v>13.4</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>68.2</v>
+        <v>52.1</v>
       </c>
       <c r="Z26" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2744,13 +2744,13 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q27" s="8" t="n">
         <v>17.6</v>
@@ -2759,13 +2759,13 @@
         <v>16</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>18.2</v>
+        <v>17.1</v>
       </c>
       <c r="T27" s="8" t="n">
-        <v>90.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="V27" s="8" t="n">
         <v>17.4</v>
@@ -2774,13 +2774,13 @@
         <v>16.7</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>95.7</v>
+        <v>93.3</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         <v>13.3</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" s="8" t="n">
         <v>22.9</v>
@@ -2844,13 +2844,13 @@
         <v>18.6</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>21.4</v>
+        <v>18.5</v>
       </c>
       <c r="T28" s="8" t="n">
-        <v>76.7</v>
+        <v>66.2</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>16.4</v>
@@ -2859,13 +2859,13 @@
         <v>15.5</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>17.6</v>
+        <v>17</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>94.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z28" s="8" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2914,19 +2914,19 @@
         <v>10.5</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>97.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>17</v>
@@ -2941,7 +2941,7 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>14.7</v>
+        <v>17.3</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>16.7</v>
@@ -3097,13 +3097,13 @@
         <v>17.3</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>19.7</v>
+        <v>16.1</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>72</v>
+        <v>58.8</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>7.7</v>
+        <v>11.3</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>19.9</v>
@@ -3112,13 +3112,13 @@
         <v>16.4</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>18.6</v>
+        <v>16.3</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>80.3</v>
+        <v>70</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3167,13 +3167,13 @@
         <v>10.2</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>98</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
@@ -3195,13 +3195,13 @@
         <v>17.6</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>20.1</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>78.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="Z32" s="8" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3250,13 +3250,13 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>98.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
@@ -3280,13 +3280,13 @@
         <v>17.9</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y33" s="8" t="n">
-        <v>91</v>
+        <v>86.5</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>16</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="N34" s="8" t="n">
         <v>17.8</v>
@@ -3365,13 +3365,13 @@
         <v>16.8</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="Y34" s="8" t="n">
-        <v>88.7</v>
+        <v>82.7</v>
       </c>
       <c r="Z34" s="8" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3420,13 +3420,13 @@
         <v>12.9</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
@@ -3450,13 +3450,13 @@
         <v>16.7</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>19</v>
+        <v>16.2</v>
       </c>
       <c r="Y35" s="8" t="n">
-        <v>77.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="Z35" s="8" t="n">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3505,13 +3505,13 @@
         <v>10.5</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
@@ -3535,13 +3535,13 @@
         <v>14.6</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>16.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>68.5</v>
+        <v>51.7</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>7.6</v>
+        <v>11.7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3673,13 +3673,13 @@
         <v>12.8</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>23.1</v>
@@ -3703,13 +3703,13 @@
         <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>18.9</v>
+        <v>16.4</v>
       </c>
       <c r="Y38" s="8" t="n">
-        <v>79.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Z38" s="8" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3758,13 +3758,13 @@
         <v>12.5</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q39" s="8" t="n">
         <v>26.6</v>
@@ -3773,13 +3773,13 @@
         <v>18</v>
       </c>
       <c r="S39" s="8" t="n">
-        <v>20.6</v>
+        <v>14.8</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>59.2</v>
+        <v>42.4</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>14.2</v>
+        <v>20.1</v>
       </c>
       <c r="V39" s="8" t="n">
         <v>21.7</v>
@@ -3788,13 +3788,13 @@
         <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>17.8</v>
+        <v>13.7</v>
       </c>
       <c r="Y39" s="8" t="n">
-        <v>68.7</v>
+        <v>52.9</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>8.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3843,19 +3843,19 @@
         <v>10.3</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>98</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="8" t="n">
         <v>22</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="S40" s="8" t="n">
         <v>18.4</v>
@@ -3873,13 +3873,13 @@
         <v>16.8</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="Y40" s="8" t="n">
-        <v>83.3</v>
+        <v>74.7</v>
       </c>
       <c r="Z40" s="8" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3928,13 +3928,13 @@
         <v>8.6</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q41" s="8" t="n">
         <v>23.4</v>
@@ -3943,13 +3943,13 @@
         <v>17.4</v>
       </c>
       <c r="S41" s="8" t="n">
-        <v>19.9</v>
+        <v>15.8</v>
       </c>
       <c r="T41" s="8" t="n">
-        <v>69</v>
+        <v>54.8</v>
       </c>
       <c r="U41" s="8" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="V41" s="8" t="n">
         <v>22</v>
@@ -3958,13 +3958,13 @@
         <v>18.5</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>21.3</v>
+        <v>18.9</v>
       </c>
       <c r="Y41" s="8" t="n">
-        <v>80.5</v>
+        <v>71.5</v>
       </c>
       <c r="Z41" s="8" t="n">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4013,13 +4013,13 @@
         <v>11.3</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>96.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q42" s="8" t="n">
         <v>26.6</v>
@@ -4028,13 +4028,13 @@
         <v>17.6</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>20.1</v>
+        <v>14</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>57.7</v>
+        <v>40.1</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>14.7</v>
+        <v>20.9</v>
       </c>
       <c r="V42" s="8" t="n">
         <v>22</v>
@@ -4252,7 +4252,7 @@
       <c r="M46" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="8" t="n">
+      <c r="N46" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4268,13 +4268,13 @@
         <v>17.7</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>20.2</v>
+        <v>15.5</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>65.09999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="V46" s="8" t="n">
         <v>21.3</v>
@@ -4283,13 +4283,13 @@
         <v>16.8</v>
       </c>
       <c r="X46" s="8" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="Y46" s="8" t="n">
-        <v>75.5</v>
+        <v>63.4</v>
       </c>
       <c r="Z46" s="8" t="n">
-        <v>6.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
